--- a/result/comment_output_1.xlsx
+++ b/result/comment_output_1.xlsx
@@ -7,26 +7,26 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV15L9jYjEVG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1yP9nYuELq" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV19u9vYwEa3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV18h9nYDES1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1259BYxENJ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1jv97YHEF9" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1LA9HYfEBs" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1K99BYfEdr" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1Gv9iYPESe" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1b29iYdEPF" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1Ds9zYBEXM" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV16A9jYWEQr" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1Ui9nY7Ejh" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1Ai9xYXEk4" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1uk9iYbEdE" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1M19iY4EjT" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1vj9EYpEW6" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1wx97YtEVT" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1Zj9nYcEvM" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1x39BYtEiB" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1RgXMYXE2X" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1eNQ8YkETA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1r1Q4YmEH7" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV11TQgYzEH3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1kmX5YQEvC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1ZHQkYJEjg" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1h5QaY5EaH" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1pvQ3YgEtU" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1SSX3YXEGL" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1LdQPYkEve" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1sDQgYgEVX" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1LfQBYBEeg" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV11DXTYiECE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1XWQbY6Ea3" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1WYQwYSEbr" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1n1QBY7E6R" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1EBQaYZEQK" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1FKQ4YLEsY" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1eGQeYWEw1" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BV1t4QiYQEMg" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,24 +478,24 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>不要踩着父母的肩膀看过世界的繁华后，又嫌弃父母的平庸</t>
+          <t>为了这碗汤，燃尽了！</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SL老五</t>
+          <t>三与三十万患者</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>保密</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>标题说的真好[支持]有些初生自己爱慕虚荣反而嫌弃自己父母没能力</t>
+          <t>00:11 可爱捏</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -508,18 +508,18 @@
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 19:56:09</t>
+          <t>2025-03-18 11:01:58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>东边的BiLi</t>
+          <t>风奇不信邪</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,9 +529,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>首先 三折叠不能代表什么 人家一样会看不起你
-其次 文化教育太重要了 这种人 一旦得势会马上开始乱来的 到时候 他要的就是私人飞机出行了
-如果再给他往上爬 他要的可就是私有小岛，领地 然后拿来当萝莉岛招呼客人了</t>
+          <t>[doge][doge]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -541,21 +539,21 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-05 10:54:39</t>
+          <t>2025-03-18 11:05:40</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>我是呢喃的人</t>
+          <t>服刑时长两年半</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,7 +563,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>我的大学生活。买课本。室友A，我在TB淘的只要8快。室友B，XXXXXXX玩意，老子6快。室友C，你们真是XXXXXXXX，我在拼夕夕买的5.99。没怎么攀比。</t>
+          <t>你的淮南牛肉汤没我的正宗[doge]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -575,14 +573,1192 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>939</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-03-18 11:11:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>杨嘚溜真帅</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>铁牛牛面[doge_金箍]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
-        <v>47</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2025-03-05 00:50:21</t>
+      <c r="G5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-03-18 11:16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>总有傻狗抢我安全距离</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>你这汤正不正宗不知道，但一定不正经[嗑瓜子]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-03-18 11:16:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>小土豆辣酱</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>我吃了没煮熟的菌子？[哦呼]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>98</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-03-18 11:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>是黄兄啊</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>我不吃牛肉[妙啊]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-03-18 11:38:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>薛定谔の投币</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>你的牛怎么有点不开心的样子[撇嘴]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-03-18 12:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>windyfalls</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>你牛肉多，我信你</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-03-18 12:07:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>月影言</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>我不喝洗澡水</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-03-18 12:08:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>李双江同志</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>你这是海南牛肉汤吧</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-03-18 12:13:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>让媳妇叫我爸爸</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>放过牛牛吧[doge]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-03-18 12:16:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>正方体混凝土</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>骇死我了[灵魂出窍]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-03-18 12:33:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>從前啊有座山</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>回复 @小土豆辣酱 :没放辣椒老牛不高兴Ծ‸Ծ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-03-18 13:05:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Earned_Not_Given</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B友什么鬼图都有</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-03-18 13:16:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>清输入呢称</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>你这🐮，有点瘦</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2025-03-18 13:18:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>腰疼贴药不管用</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>你把他睡了？他这样看你</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025-03-18 14:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>绕着地球做圆周</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>感觉你这个牛肉汤是云南的啊</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2025-03-18 14:43:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>我一点也不伤心</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>我们淮南牛肉汤里不放牛牛，谢谢[微笑]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2025-03-18 14:53:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>快哥giggity</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>对牛哥犯错了</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2025-03-18 14:55:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>JoJohnny烨</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>一整头牛也太奢侈了[惊讶]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2025-03-18 14:59:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>祈盼天下大同</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>有牛，有肉，还有面，太正宗了[笑哭][笑哭]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2025-03-18 15:03:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>毒萄</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>我嘞个牛牛泡澡汤[笑哭]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2025-03-18 15:09:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>新島真天下第一</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>没豆饼还加面？[生气]假！</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2025-03-18 15:44:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>氟利昂卖茶人</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>布什戈门，什么家庭啊，一顿吃一头牛？[惊讶]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2025-03-18 15:51:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>声sheng催天雨</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>淮南牛牛汤</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:23:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>终极呆头鹅</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>难蚌啊[笑哭]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:36:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>嫁给我吧常陆茉子</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>你把这张图给淮南人看，再说你这句话，不红温挑战你包赢的[doge]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:37:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>山野村夫003</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>牛马何苦为难牛[doge_金箍]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:40:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>发起疯来连自己都吃</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>回复 @小土豆辣酱 :不，是菌子把你吃了[doge]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:43:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>卡塞尔学院狮心会</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>你这是云南牛肉汤吧</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:45:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>天真少年爱红颜</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>你越这样我越兴奋！[点赞]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:56:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>黑马户狸户</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>我就说多看评论区能刷到好东西[脱单doge]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2025-03-18 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>荒古姥姥</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>回复 @小土豆辣酱 :手机也吃菌子啊</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>服刑时长两年半</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2025-03-18 17:08:22</t>
         </is>
       </c>
     </row>
@@ -643,14 +1819,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>学校虽小，梦想很大，希望孩子们快乐学习，茁壮成长。</t>
+          <t>《超极限级の考生》</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DDDbbbz</t>
+          <t>阵列豹</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -660,7 +1836,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[doge]想被夸帅</t>
+          <t>这种人拿到驾照难道不是恐怖故事吗[捂脸]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -673,18 +1849,18 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>214</v>
+        <v>1162</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-05 15:07:52</t>
+          <t>2025-03-17 12:31:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>渡渡渡渡时</t>
+          <t>出木杉-英才</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -694,7 +1870,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>刚哥好，我就是专门做塑胶的，也是湖北人，如果长期使用还是建议做塑胶，这个草坪一看就是自己施工的，管不了多久，不过学校没几个孩子换不换也没必要了，如果有这方面需要，也可以联系，到时候可以直接按成本施工，我不赚钱也当尽善了，毕竟我也是打工的，也欢迎来湖北[打call]</t>
+          <t>看见交警想着自己没带头盔，赶紧下来推车[星星眼]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -704,31 +1880,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>5144</v>
+        <v>861</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-04 22:23:53</t>
+          <t>2025-03-17 12:21:55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>风起之时341</t>
+          <t>利不留锋</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>保密</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>曾经也是留守儿童，现今在大城市打拼，梦想将这里的一瓢水带回家乡。</t>
+          <t>没学过车，我问一问，这操作很逆天吗？[笑哭]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -738,14 +1914,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>1270</v>
+        <v>3030</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-04 21:14:23</t>
+          <t>2025-03-17 12:03:44</t>
         </is>
       </c>
     </row>
@@ -806,24 +1982,24 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>我刚被注射完死刑就抓到真凶了，还能抢救吗？</t>
+          <t>升级操场不是说说而已，希望这个操场能让孩子们享受运动，爱上体育。</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>方舟拆迁大队</t>
+          <t>胡桃桃啊1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>那我要是用内力把注射液从我的经脉中排出呢</t>
+          <t>真的很佩服这些到农村的小学当校长的，我小时候学校贼破，来了个看着二三十岁的校长，学校一年比一年好，后来一年300块学校管一学期的午饭晚饭，校长天天在那用一口大锅做饭，经常有毛肚芦笋什么的比较贵的食材，量还比较大，从那毕业十几年了，过年回家路过看了一眼，校区大了好多，多了两栋两层的楼，看起来一个是餐厅一个是宿舍，教室的玻璃也不像小时候那样一堆洞冬天冻的要死了，有天校长来找我妈商量事情，一个四十多岁的人看着跟五十多一样，这十几年不知道他操了多少心</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -836,18 +2012,18 @@
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>7141</v>
+        <v>1061</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 01:07:48</t>
+          <t>2025-03-14 17:42:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>就不设置昵称了</t>
+          <t>东风曳放花千树</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -857,7 +2033,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>第一，律师已经解释了，没机会抢救。第二，哪怕真凶认这个罪，法官也不会认，想翻案，怕是得折腾二十年</t>
+          <t>慕名而来。年纪轻轻就染上蜗丧德，前途一片光明啊。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -867,21 +2043,21 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>1231</v>
+        <v>46</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-03 20:26:32</t>
+          <t>2025-03-17 12:52:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>永恒之外的叙事者</t>
+          <t>原子弓单下无冤魂</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -891,8 +2067,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>我记得欧美那块过去贼迷信，如果绞刑没绞死会当成上帝寻思犯人不该死，然后这个犯人就能被免于处决了。
-也就是现在不整这套了，不然那个耐活王说不定真的能苟到被赦免[脱单doge]</t>
+          <t>但行好事，莫问前程[调皮]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -902,14 +2077,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>430</v>
+        <v>98</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-03 21:22:05</t>
+          <t>2025-03-15 23:20:49</t>
         </is>
       </c>
     </row>
@@ -970,27 +2145,24 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>超乎想象的青雀1金0t天谴之矛！奇迹还在延续！四星亦可登神！</t>
+          <t>画画很多年，从不喜画卡通动漫人物，但是哪吒、悟空这样中国的神话人物，我喜欢，必须画！</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>托帕总监_love</t>
+          <t>汐汐宝贝喜欢喝豆浆吖</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>《“塔青”两极冷战背景下经济体系》下各国货币汇率统计：（3月3日）
-1黑塔币=1青雀币=2阿雅币=2飞霄币=2翡翠币=3云璃币=3黄泉币=4小黑塔币=4雪衣币=4记忆主币= 4景元币 =4希露瓦币=5饮月币=5银枝币=5希儿币=6流萤币=6镜流币=7缇宝币=7刃币=7阿兰币=7乱破币=8波提欧币=9（10）真理币=9dot币=9灵砂币=10忘归人币=10通解币（佩拉）=10符玄币=11知更鸟币=13卡芙卡币=14砂金币=14真托追击币=17丹恒币=18量子币=19虎克缇宝币=19（26）瓦尔特币=21公司币（砂翡）=22托帕币=23（34）克拉拉币=23（30)银狼币=26银狼币=31罗刹币=31虎克币=36（43）姬子币=41（48）彦卿币=41轮椅币（三月七）
-星际和平公司战略投资部
-（注）括号内的币为常驻（或免费赠送）+限定的总计</t>
+          <t>相信梦想是价值的源泉，相信眼光决定未来的一切，相信成功的信念比成功本身更重要，相信人生有挫折没有失败，相信生命的质量来自决不妥协的信念。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1000,21 +2172,21 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 11:58:29</t>
+          <t>2025-03-18 14:38:58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>让我滚去写轻小说</t>
+          <t>主页收蔵看小紫妹妹</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1024,7 +2196,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>😃👆我知道你在找谁</t>
+          <t>鹤望兰美，花如仙鹤</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1034,34 +2206,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>1812</v>
+        <v>52</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-04 12:15:51</t>
+          <t>2025-03-18 15:04:15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>一只会咕咕叫的狂风</t>
+          <t>主页收蔵看小紫妹妹</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>致敬。
-虽然不用青雀
-但看到这个鬼畜的轴和凹度
-我觉得我必须支付观看这个视频的费用</t>
+          <t>战国时期的百家争鸣，除儒道之外，法家以法治国，商鞅变法使秦国崛起；墨家兼爱非攻，倡导和平与互助。不同学派观点碰撞，为中国思想文化发展注入强大活力。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -1071,14 +2240,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>7346</v>
+        <v>53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-04 14:08:58</t>
+          <t>2025-03-18 15:11:52</t>
         </is>
       </c>
     </row>
@@ -1139,24 +2308,24 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2年烧掉40亿！曾经红极一时的无人超市，为啥消失了？</t>
+          <t>那些绝对不可能在爸妈面前做的事！</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-__-Maverick-__-</t>
+          <t>MY_LM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>保密</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>看到个采访，大妈已经给出答案了：“无人超市有啥好处？” 记者：“不用招售货员，可以节省成本” 大妈：“节省成本了买东西能便宜吗？” 记者：“。。。”</t>
+          <t>孩子们，想我了吗？[doge]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1169,18 +2338,18 @@
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-05 14:09:50</t>
+          <t>2025-03-17 22:48:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>侦探快斗</t>
+          <t>小峯大叔</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1190,7 +2359,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>自动售卖机都出了多少年了。无人超市里放满各种自动售卖机怎么样[滑稽]那不也是无人超市。</t>
+          <t>从高温30度
+急降到10度
+先泡熟，捞出来立刻泡冰水
+利用热胀冷缩原理，让皮肤收缩紧致
+一道皮脆肉嫩的白切鸡就做好了</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1203,18 +2376,18 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>1089</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-04 23:27:52</t>
+          <t>2025-03-17 21:20:20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>四大流量卡办理</t>
+          <t>茨木贼可爱</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1224,7 +2397,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>别的专业不懂，我学的是工商企业管理无人超市真研究过。最基本原因就2个，一个中国人力成本太低；第二个就是超市是服务业，没有服务员算什么服务，冷冰冰的机器还不如去网购[吃瓜][吃瓜][吃瓜]</t>
+          <t>要在广州市里，人民路的蜜雪冰城，大概只有这一家了[笑哭]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -1237,11 +2410,11 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>1079</v>
+        <v>374</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-04 17:56:45</t>
+          <t>2025-03-17 22:44:11</t>
         </is>
       </c>
     </row>
@@ -1302,24 +2475,24 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>德爷荒野求生收官之战 能否将挨饿进行到底！《单挑荒野：水之章》</t>
+          <t>在它们手里就没有不费的东西，一年拆一个</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>阿川Ss</t>
+          <t>查無x此人</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>这一章纳米比亚里面，德爷想起了家人这一点上可以说是荒野生存巨大动力源之一，记得当年贝爷也说过，类似的话，就是如果求生中遇到很痛苦的事情，就想想在家里面的家人也就度过了，不过贝爷那个比较难蹦，因为他是在海岛那一期贝比沉上示范灌肠的时候说的[笑哭]</t>
+          <t>哈哈哈哈二毛把情绪写在脸上了[吃瓜]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1332,28 +2505,28 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>252</v>
+        <v>111</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-05 15:28:23</t>
+          <t>2025-03-16 11:27:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>三月忘川风华</t>
+          <t>扬沙_Ethereal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>保密</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>德爷还在拍</t>
+          <t>up能不能做一个直径一米八左右的这个，我家猫有点大说是，拜托了[保佑]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1363,31 +2536,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4805</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-05 17:12:44</t>
+          <t>2025-03-17 01:05:53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>浮华live至尊</t>
+          <t>我是鸽子君图</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>从德爷账号的最新情况来看后面还会出火之章土之章[星星眼]</t>
+          <t>主人手巧，猫猫也粘人，好温馨的感觉。我跟我家猫就好像那个邻居，他白天搁我床底下睡觉，晚上搁我被子上睡觉，偶尔起床吃饭喝水，平时见面就互相点个头就过去了，他也不来蹭我，我也摸不到他[藏狐]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -1397,14 +2570,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>172</v>
+        <v>432</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-05 15:36:34</t>
+          <t>2025-03-16 21:10:22</t>
         </is>
       </c>
     </row>
@@ -1465,14 +2638,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>它的发明，让每次“逆行”都有了安全归来的勇气 。</t>
+          <t>当AI搜索结果一本正经瞎编时，你真的能分得清吗？【差评君】</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>阴守四方</t>
+          <t>小忍秘密行动</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1482,7 +2655,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>我觉得可以说这个发明有缺陷不完美，但不能否认是伟大的发明，伟大的发明不是完不完美，而是开创先锋</t>
+          <t>AI并非坚不可摧[doge]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1492,31 +2665,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>2496</v>
+        <v>83</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 13:16:16</t>
+          <t>2025-03-17 15:41:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>腐癌滚出太阳系</t>
+          <t>索索纳杠西</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>致敬传奇大聪明[doge]</t>
+          <t>[支持]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1526,31 +2699,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>156</v>
+        <v>898</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-04 07:22:51</t>
+          <t>2025-03-17 11:17:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>小林家的死亡之翼</t>
+          <t>阿斯顿福贵猫猫头</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>我记得我初中刚接触化学的时候靠惊世智慧想出了一个点子，那就是往火场里面灌氢气，氢气和氧气反应会生成水，正好可以灭火</t>
+          <t>chatgpt的答案只有80分左右的样子。deepseek的思考过程能打95分以上，但是输出的答案也有65分的样子。于是我把deepseek的思考过程喂给chatgpt，于是就有了90分以上的回答[doge_金箍]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -1560,14 +2733,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>2008</v>
+        <v>646</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-04 22:47:03</t>
+          <t>2025-03-17 09:15:10</t>
         </is>
       </c>
     </row>
@@ -1628,14 +2801,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>66岁的姨无人能挡</t>
+          <t>【NMIXX】“KNOW ABOUT ME” M/V</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>我还是去好好学习叭</t>
+          <t>大家的音乐机</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1645,7 +2818,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>建议叔叔阿姨买个护腰[星星眼]阿姨加油[星星眼]</t>
+          <t>NMIXX迷你四辑主打曲《KNOW ABOUT ME》MV上线啦～来参与二创活动，有机会获得【签名专辑】～欢迎带话题#NMIXX新歌KNOWABOUTME安利#，发布翻唱、翻跳、演奏、MV reaction、混剪等音乐舞蹈内容，创作形式不限～[星星眼]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1658,28 +2831,28 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>3155</v>
+        <v>2783</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 00:58:33</t>
+          <t>2025-03-17 17:05:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>也冬</t>
+          <t>爻爻日记nmaaixx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>您真是抽象届一股清流，这梗密集、接地气，还不庸俗，真的佩服</t>
+          <t>各位恩瑟有melon账号的努努力按图片的歌单切瓜！有能力的也可以找找代切切瓜！现在音源稍稍不太妙 大家努努力！</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1689,21 +2862,21 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1114</v>
+        <v>40</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-04 22:41:16</t>
+          <t>2025-03-18 11:51:28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>对话寂静</t>
+          <t>玛卡巴卡有个小推车_</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1713,7 +2886,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>放下助人情结 尊重他人命运 逆子就别管了 攒下来的钱等老了拿去环游世界</t>
+          <t>之前主打拼接说吵、生硬，这次拼得既流畅又丝滑，mix和 easy listening全要了又说平，到底要小爻爻怎样[微笑]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -1726,11 +2899,11 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>298</v>
+        <v>2284</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-05 01:45:40</t>
+          <t>2025-03-17 17:14:24</t>
         </is>
       </c>
     </row>
@@ -1791,24 +2964,25 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>我不服气！我决定向这个可恶的三次元宣战！</t>
+          <t>笑啊? 你怎么不笑啦！2024 年度新番打脸大总结！【泛式】</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>阿sir我今天真没开摆</t>
+          <t>是薄荷兔呦</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>上班了之后越来越能理解日本那些大叔为什么愿意疯狂的应援一些偶像  死水搬的日常注入一模缕阳光真的很重要</t>
+          <t>https://x.com/mori_masa_/status/1895056168416170083?t=xAmNILJOy-PfkGx94UCGDw&amp;amp;s=19
+泛式啊你在油管的舔甜歌姬解說 被哎咕島的導演分享到推特了[doge]（某種程度上 導演認可了泛式</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1821,28 +2995,28 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>6462</v>
+        <v>455</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-05 07:42:45</t>
+          <t>2025-03-16 20:34:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>木m鹿</t>
+          <t>免费烧水</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>看完这个视频感觉自己的尸体活力满满，但是就是不想动</t>
+          <t>真的搞笑我说最喜欢艾莉的居然是第一集，他让我别带丰川祥子节奏</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1852,21 +3026,21 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>4024</v>
+        <v>1918</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-05 02:48:08</t>
+          <t>2025-03-16 20:59:20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>我饿了但不吃</t>
+          <t>绳网用户-芙宁娜</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1876,7 +3050,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>小时候我总感觉二次元应该是穿着漂亮衣服活力满满会大声讨论自己热爱的小男孩女孩，而不是现在什么婆罗门和厕妹。。[大哭]</t>
+          <t>有的兄弟，有的[点赞][点赞]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -1886,14 +3060,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>2715</v>
+        <v>216</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-05 07:11:21</t>
+          <t>2025-03-16 20:37:08</t>
         </is>
       </c>
     </row>
@@ -1954,14 +3128,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>呐~你是许了让自己变傻的愿望吗？</t>
+          <t>正史还能比野史还野吗？能</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>愿人无事</t>
+          <t>勾脚老太爷邓肯</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1971,7 +3145,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>在这里放个芙芙，祝大家和我抽芙芙十连三金不歪[打call]也是终于能把四命芙芙补满了</t>
+          <t>李白带着杜甫修仙[doge]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1981,31 +3155,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>4542</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 17:46:01</t>
+          <t>2025-03-16 11:38:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>帕岛艾-残暴心</t>
+          <t>beiyeah561</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>甜到无法形容的了[大哭][打call][给心心]（再给各位补一张甜点[滑稽][滑稽][吃瓜]）</t>
+          <t>还有苻坚的“一雌复一雄，双飞入紫宫”的故事，慕容冲和他的亲姐姐清河公主，都才十几岁，被一并纳入后宫[doge]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2015,31 +3189,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>3288</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-04 18:16:23</t>
+          <t>2025-03-16 11:53:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>梓川桜太</t>
+          <t>万能下划线</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>我们始终不知道，up究竟是经历了什么，才能每次都做的这么自然这么甜蜜🥰</t>
+          <t>那下期就来一点看似是正史实则是野史的东西吧[妙啊]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -2049,14 +3223,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>1092</v>
+        <v>8607</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-04 17:25:43</t>
+          <t>2025-03-16 11:48:16</t>
         </is>
       </c>
     </row>
@@ -2117,14 +3291,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>《明日方舟》干员「死芒」技能展示PV</t>
+          <t>90s挑战花招百出的造假工艺</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>浮生眠光</t>
+          <t>家住佩斯利公园</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2134,7 +3308,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>特别注明：在二技能在H11-4的演示中，之所以面板攻击力是729，是因为下面有个三模小羊的22加攻</t>
+          <t>我还以为今年315会曝光手机虚拟号码黑产业链呢，看来大家都不怕被骚扰。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -2144,21 +3318,21 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>10310</v>
+        <v>386</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 18:41:03</t>
+          <t>2025-03-17 13:02:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>生鱼有患死鱼安乐</t>
+          <t>Vick维克丶</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2168,7 +3342,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>这是单给她一个的，还是后续干员都有？</t>
+          <t>等一下，这个视频什么意思？老百姓为了生活疲于奔命，还要让老百姓在购物的时候学会甄别？而不是有关部门的监管？</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2178,31 +3352,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>13381</v>
+        <v>51</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-04 17:46:33</t>
+          <t>2025-03-18 10:22:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nolivita_</t>
+          <t>爱卿丶小生</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>破案了原来死芒是设计师的代号，TA一定要带着这个代号一条路没有NG的走下去[汤圆]</t>
+          <t>这个视频的初衷不是真的让水哥去找出来，而是侧面表达出 连水哥都无法分辨，那我们普通人又怎么辨真假呢</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -2212,14 +3386,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>6348</v>
+        <v>1185</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-04 21:05:27</t>
+          <t>2025-03-17 12:43:02</t>
         </is>
       </c>
     </row>
@@ -2234,7 +3408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2280,14 +3454,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>我在接龙游戏开发里拿了MVP</t>
+          <t>315晚会年年有新料，我们的食品安全会好吗？</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NuZhAo</t>
+          <t>一觉醒来发现是梦</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2297,7 +3471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>最后居然没有总结互相甩锅环节我是不认可的，等到最后就黑屏几秒钟[doge]</t>
+          <t>这不得先去学校食堂查查，天天都说食堂特别健康，安全，麻烦看看食堂有多安全[doge]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -2310,18 +3484,18 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
+        <v>263</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-05 11:41:48</t>
+          <t>2025-03-18 08:05:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M木糖M</t>
+          <t>Spirit-YZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2331,31 +3505,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>小小尝试</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>我们学校食堂挺正常的 每个窗口的食品都会留样</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>一觉醒来发现是梦</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>一级评论</t>
+          <t>二级评论</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>1136</v>
+        <v>11</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-05 11:05:35</t>
+          <t>2025-03-18 15:26:20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>icewater冰水</t>
+          <t>骚milk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2365,24 +3543,1578 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>非常好想法 要是有个几个制作者最后对着成品交流吐槽的环节就好了！</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>你怎么知道我今天中午吃完现在肠胃炎犯了</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>一觉醒来发现是梦</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:06:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>不放香菜不放葱_official</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>太真实了，我吃外卖不拉肚子，吃食堂拉，好几回了[笑哭]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>一觉醒来发现是梦</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:17:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>你也会软弱i</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>没吃死人就是小事</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>一觉醒来发现是梦</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:26:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>明轩天小六</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>回复 @不放香菜不放葱_official :食堂蛋白质多助消化[吃瓜]外卖都的杀死了除了喷射套餐</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>一觉醒来发现是梦</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:36:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>不放香菜不放葱_official</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>回复 @明轩天小六 :主要是食材不是很新鲜，上次吃的西红柿炒鸡蛋里的西红柿已经有坏掉的味道了，食堂的员工也是照样做</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>一觉醒来发现是梦</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:48:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>浮幽樱花</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>以前在厂子里上班的时候，我这钢肠铁胃竟然能吃出急性肠炎，辞了职以后怎么吃外卖都没犯过病[捂脸]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>一觉醒来发现是梦</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-03-18 17:14:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>常常吓到人的小透明</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>回复 @Spirit-YZ :我之前的一个学校食堂也留样，但架不住里面总能出现一些不属于菜的东西（什么钢丝球，铁丝啥的，我吃到过鸡的气管，没有经过很细的清洗加工，导致菜的味道很怪[捂脸]）</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>一觉醒来发现是梦</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-03-18 17:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>一百抽五张五星光锥</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>我学校就有那些监管的人来了[思考]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>一觉醒来发现是梦</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-03-18 17:27:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FindSometingFun</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>回复 @Spirit-YZ :特指中学食堂</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>一觉醒来发现是梦</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-03-18 17:36:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>不阴阳怪气，我个人就是会认为中国的食品安全可能不是全球最好的，但绝对是最领先的一批。看似能暴露出很多的问题更多是因为现在网络更加发达。而且从另一个侧面现象也能多少反映出我的观点，就是目前恶意抹黑我们的国家食品安全的造谣事件越来越多，多是因为某些大国在各种方面的竞争力开始慢慢不如我们，明着打压又打不过，就开始以这种文化渗透的方式从内部去挑起我们自己的质疑。就比如说各种食品科学，实际上都是各种相关领域的大佬各种苦心研发开发搞出来的新品种然后打破垄断之类的，反而会被恶意抹黑成“科技与狠活”，最近的不是就一个打破白羽鸡种鸡的垄断，就是辛苦搞了几年的科技成果，不止是我们摆脱了漂亮国的垄断，而且让周边国家也不从漂亮国进货了，改从我们这，那他们怎么办嘛，就是用这种舆论渗透，开始潜移默化引导我们这边说啊这种鸡都是什么科技狠活鸡，都是打什么激素什么的各种抹黑就是了，怎么就是怎么威胁我们的粮食安全怎么来。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>一级评论</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2450</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2025-03-05 11:13:07</t>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>97</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-03-16 19:15:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>而且，目前国内能曝光出来各种真实的食品安全事件，又不是其它国家就没有，无非我们平时不容易接触到而已，况且我们国家这么大，人口这么多，管理难度本来就是远超他国的，首先要养活这么多人本身就不是那么容易的事</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-03-16 19:18:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>朋城雪夜</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[笑哭]别人好不好跟我没关系，什么时候让我们自己放心就行，但现在我不放心</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-03-16 19:20:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>大爱Fluttershy</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>毕竟咋们国家在国家排行都是遥遥领先的，虽然还是发展中国家，人口基数极大，但并不妨碍我国更好的找到错误并且更正，只不过更加困难而已</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-03-16 19:23:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>麻绳李公</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>回复 @朋城雪夜 :那就少看一些营销号制造的焦虑，要知道合格的才是绝对的大多数，一大张白纸不能只盯着黑点看。就像路上每天都有交通事故，没见谁焦虑的不敢出门。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2025-03-16 19:27:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BeeKnight</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>当你一张嘴说某大国的时候。我是真的觉得你在阴阳怪气。</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025-03-16 20:00:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>回复 @BeeKnight : [滑稽]只不过阴阳的对象不是我们</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2025-03-16 20:37:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>朋城雪夜</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>回复 @麻绳李公 :路上的交通事故一年就看见一起，食品不卫生是天天经历啊[笑哭]。尤其你是学生时候去兼职后厨，除了肯德基之类的，没看见一个干净的</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2025-03-16 21:08:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>獨對今晚月半彎</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>我不是质疑你，我问问你这个中国包括港澳台和特殊人群吗？你要知道我们普通人的食物跟以上我提到的是两种食物。</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2025-03-16 22:14:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mr.Limit</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>回复 @獨對今晚月半彎 :台湾自己问题多多就先不说了，那你对供港澳食物有特殊滤镜的话，那岂不是就送了个把柄给商家吗？只要标的是供港/澳、甚至是中央采购的食物，再贵你也愿意去买咯？那大有文章可做[吃瓜]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2025-03-16 23:01:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>足彩预言家</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>哈哈哈哈哈哈哈哈哈哈哈</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2025-03-17 07:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>我的玩具都活了</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>哈哈哈哈哈哈哈哈</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2025-03-17 08:50:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>我的玩具都活了</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>还是三鹿牛奶喝太少了，还没真的打疼导致的</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2025-03-17 08:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>康先生123</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>问题来了，是麦当劳吃的放心还是兰州拉面卫生？？？？</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2025-03-17 09:47:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lyamtrak</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>有病</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2025-03-17 10:52:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>我的名字就要起这么长</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>去街上任何一个排挡打个工吧[doge]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2025-03-17 11:43:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>上任康城丶</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>你开心就好</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2025-03-17 12:22:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BeeKnight</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>回复 @囧勒个狼 :美国掩盖中国食品问题：美国不想中国人吃好。美国揭露中国食品问题：美国扰乱中国的食品行业。美国不管不顾：美国自身难保。主打一个立体防御。真是给我整乐，天天一些b学生五指不沾阳春水，肩不能扛手不能提，吃爸妈穿爸妈，还有些大专 臭高中的，也来发表宏大叙事是真抽象。</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2025-03-17 13:42:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>羊仁王</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>你是没吃过是食堂还是没下过馆子</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2025-03-18 06:53:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>退网了_哥们</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>你的回复里已经开始刷怪了</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2025-03-18 10:39:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>柚梓杋</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>我勒个仙之人兮列如麻</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2025-03-18 10:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>退网了_哥们</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>回复 @康先生123 :热知识，中国的肯德基麦当劳都算是国企</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2025-03-18 11:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Mr.Limit</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>回复 @康先生123 :我吃兰州拉面窜过，金拱门开封菜至今很正常。</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2025-03-18 11:38:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hxsuc</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>回复 @我的玩具都活了 :你是日本森永喝少了[给心心]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2025-03-18 11:53:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>迈克儿本山</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>去趟超市各种字都印不清楚的小食品就在哪摆着。你说的刻意抹黑在哪呢？举个例子</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2025-03-18 15:49:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>新保_弘</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>我袁承志为新的食品安全圣经。</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2025-03-18 16:31:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>萌星哦哦</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>回复 @Mr.Limit :kfc我也窜过，这种冰可乐+热炸鸡就是容易窜</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>囧勒个狼</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2025-03-18 17:34:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>学医救不了主C</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>没有新料才是最恐怖的</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>一级评论</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>737</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2025-03-17 15:56:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>倾城TRUST</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>那确实</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>学医救不了主C</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>19</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2025-03-17 16:52:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>石墨子coco</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>今年电诈，线缆甚至都可以从以前的315中看见身影的</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>学医救不了主C</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>17</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2025-03-17 18:13:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>一万次就好</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>密码的，检测有问题你要喷，检测没问题你又要说更可怕，反正就是有问题呗，你自己回深山老林种地算了</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>学医救不了主C</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>77</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2025-03-17 19:31:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>李23456789</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>回复 @一万次就好 :他说的是重复出现问题</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>学医救不了主C</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>60</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2025-03-17 20:06:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>掌柜炸酱面</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>有些人在这洗的飞起，本来就是315查封最大怎么说？平时有多少查封的？</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>学医救不了主C</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2025-03-18 13:49:00</t>
         </is>
       </c>
     </row>
@@ -2443,14 +5175,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>《九族消消乐》</t>
+          <t>TES先锋赛单曲《滔搏陀螺》</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>墨_咖</t>
+          <t>蔚蓝边际</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2460,11 +5192,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>天子赈灾开粮仓
-官员私贩赈灾粮
-灾粮变钱多费事
-何不发钱给官员
-我是王维诗里的红豆啊[调皮]</t>
+          <t>厉害，好汀[打call]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -2477,31 +5205,28 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>3124</v>
+        <v>1193</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 17:26:28</t>
+          <t>2025-03-17 21:57:56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pinoko桑</t>
+          <t>想成为传说</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>火线有电不是火
-电线短路便着火
-玩电着火多费事
-不如当初就玩火</t>
+          <t>为什么LPL能拿冠呢？因为有韩员。那为什么2024全花班“棋差一招”呢，因为没有对线。现在强制换线加全局BP再加韩员大量回去，真正属于LPL的实力要展现出来了[星星眼]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2514,31 +5239,28 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>873</v>
+        <v>22</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-04 20:04:21</t>
+          <t>2025-03-18 09:20:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>小默fanstic</t>
+          <t>唔哩大培根</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>圣上是神不是人，
-救苦救难入凡尘，
-神仙变人多费事，
-不如下凡便是神[doge_金箍]</t>
+          <t>要是石油杯那就是沙漠螺陀[吃瓜]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -2551,11 +5273,11 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>3771</v>
+        <v>502</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-04 19:47:04</t>
+          <t>2025-03-17 17:22:26</t>
         </is>
       </c>
     </row>
@@ -2570,7 +5292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2616,7 +5338,109 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>宋亚轩直播全程回顾：春日欢乐颂【2025时代少年团系列直播】</t>
+          <t>其实你根本不会用AI！指令就得这么玩</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>菠萝树上的菠萝蜜</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>确实好用，去年的公选课论文和今年的开题报告都是夸克帮我写的[tv_点赞]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>一级评论</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>240</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-03-16 12:28:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>一颗草莓汤圆</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AI PPT免费的，不用白不用，u1s1挺好用的</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>一级评论</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>257</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-03-16 18:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>这个昵称还有人用过妈</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>好视频，支持一下</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>一级评论</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>212</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-03-16 12:08:05</t>
         </is>
       </c>
     </row>
@@ -2631,7 +5455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2677,14 +5501,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>《人 类 最 不 爽 的 一 集》</t>
+          <t>《胜利女神：新的希望》前哨测试PV「虚假的乐园」</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>从小就白头</t>
+          <t>腾讯招聘</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2694,7 +5518,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[捂脸][捂脸]</t>
+          <t>集合了[腾讯招聘_鹅的大手]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -2704,55 +5528,59 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 23:32:23</t>
+          <t>2025-03-17 15:30:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>津轻斯夫斯基</t>
+          <t>悠语莱卡</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>别笑，真人真事🙃</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>抓[腾讯招聘_鹅的大手][腾讯招聘_鹅的大手][腾讯招聘_鹅的大手]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>一级评论</t>
+          <t>二级评论</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>759</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-05 01:16:55</t>
+          <t>2025-03-17 15:32:58</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>无敌神皇冠军</t>
+          <t>断小念</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2762,24 +5590,514 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>这个我前天才试过，我家二楼和三楼厕所的管道是联通的，就导致如果同时使用的话厕所的水就会逆流冲回来，前天在我上大号的时候我姐在三楼用厕所结果冲下来的水把我冲下去的史顶上来了[笑哭]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>[腾讯招聘_惊呆][腾讯招聘_鹅的大手][腾讯招聘_鹅的大手][腾讯招聘_鹅的大手][腾讯招聘_鹅的大手]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-03-17 15:40:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NOMADyy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[腾讯招聘_鹅的大手][腾讯招聘_鹅的大手][腾讯招聘_鹅的大手][腾讯招聘_鹅的大手]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-03-17 15:45:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>胜利女神新的希望</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ezi听说你也想要测试资格[doge]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>58</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-03-17 15:50:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>回复 @胜利女神新的希望 : 给我一个我什么都愿意做的！[腾讯招聘_害羞]28号来看我直播大战莱彻[阴险]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-03-17 15:54:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>北秋执城</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>不是哥们？</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-03-17 16:20:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>紫霄飘渺啊</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>招我这个传奇指挥官不[doge]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-03-17 16:22:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>unlucky-bin</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>唉，腾讯的大手</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-03-17 16:47:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>奇虎小月牙</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>你是？[腾讯招聘_外头站着]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-03-17 16:57:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>在抖我的菜我就</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>回复 @胜利女神新的希望 :能不能联动一下瞳子！</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-03-17 16:59:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>在抖我的菜我就</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>保密</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>回复 @腾讯招聘 :ezi[腾讯招聘_嘲笑]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-03-17 17:00:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ank丿维侭</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>回复 @腾讯招聘 : [吃瓜]可以先直播国际服</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-03-17 19:06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Owl-Dusty</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[腾讯招聘_惊呆][腾讯招聘_惊呆][腾讯招聘_惊呆]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>腾讯招聘</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>二级评论</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-03-17 22:43:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>坦拓織改</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>玩国服，送秋衣秋裤</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>一级评论</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>204</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2025-03-04 18:17:30</t>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-03-17 14:32:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Revive点</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>补药被骗了，这才是真正的强度榜[Mygo表情包_生气]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>一级评论</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>34</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2025-03-17 15:20:45</t>
         </is>
       </c>
     </row>
@@ -2840,14 +6158,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>《鸣潮》共鸣者「布兰特」PV | 一出好戏</t>
+          <t>《小杨有约12#》：羊头彩虹人</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>镜平章</t>
+          <t>小潮院长</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2857,7 +6175,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>之前一直看不清楚，原来船长帽子上的纹理做得这么细致！还有光照下才会显现出来的暗纹！</t>
+          <t>我不会不讨厌你的，小杨。加油！</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -2867,31 +6185,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>644</v>
+        <v>4479</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 12:34:14</t>
+          <t>2025-03-18 14:30:47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>易小寒kw</t>
+          <t>舒魇Ares</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>放心吧船长，翡萨烈对你们做的坏事，我一定会在他们家主身上加倍讨还[支持]</t>
+          <t>这一幕真的笑死我了哈哈哈哈谁懂哈哈哈哈哈哈哈哈哈哈哈哈哈哈哈哈哈哈哈哈</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2901,31 +6219,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-04 11:20:17</t>
+          <t>2025-03-18 14:05:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>山荷无恙</t>
+          <t>御坂10669号</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>祝抽布兰特的漂泊者十连三金[星星眼][鸣潮_嘿]</t>
+          <t>我不太同意“羊头人皮套下可以是任何人”耶，羊头人的声音已经腌入味了，况且这幽默感不是随便一个人都能有的</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -2938,11 +6256,11 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>499</v>
+        <v>1702</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-04 11:01:52</t>
+          <t>2025-03-18 14:34:23</t>
         </is>
       </c>
     </row>
@@ -3003,14 +6321,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>【亚某爆料时间】阿轲-化蝶舞源梦皮肤爆料来了！</t>
+          <t>直接赛场出现的失误#台球 #这台球一打一个不吱声</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LOGYT-Eberk</t>
+          <t>次情贝</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3020,7 +6338,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>我会一直视奸你👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️👁️</t>
+          <t>报名费比台费便宜</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -3033,18 +6351,18 @@
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>2887</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-05 15:20:05</t>
+          <t>2025-03-17 18:11:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>杨道理不吵架</t>
+          <t>Mo_墨城</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3054,7 +6372,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>好漂亮！源梦YYDS！！</t>
+          <t>没玩过台球，看着像是裁判的入职考试吧，两位考官技术很厉害，考生给出的答案很果断。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -3067,28 +6385,28 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>3399</v>
+        <v>993</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-05 12:06:32</t>
+          <t>2025-03-18 12:49:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>华北浪漫革命l</t>
+          <t>热心市民小达</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>保密</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>修复杨玉环星之鸣奏实战随机行走动作粒子特效丢失，被动全屏切换粒子特效丢失</t>
+          <t>一想到他们两个有一个人能赢我就浑身难受[doge][doge][doge]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -3101,11 +6419,11 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-05 12:00:57</t>
+          <t>2025-03-18 01:34:06</t>
         </is>
       </c>
     </row>
@@ -3166,14 +6484,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>当我们拍芙宁娜时，我们在拍什么？</t>
+          <t>TES先锋赛单曲1.0《突然的陀螺》</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>语堂天天啃土</t>
+          <t>黑神话の高手と楊間</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3183,7 +6501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>纯粹的 ——— 好！看！</t>
+          <t>郭浩：杰克，就剩咱俩了，我怀疑我是内鬼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -3193,21 +6511,21 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>1225</v>
+        <v>124</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-05 01:06:36</t>
+          <t>2025-03-17 20:07:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>栢熙熙熙熙</t>
+          <t>60分及格了哦</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3217,7 +6535,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>分享一下去年的拍照活动拍的！我很满意的一张，但是苦于不会后期哈哈哈哈[保卫萝卜_哇][保卫萝卜_哇]</t>
+          <t>我们会创造新的历史</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -3227,31 +6545,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>298</v>
+        <v>39</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-05 03:17:24</t>
+          <t>2025-03-17 15:06:59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2333417111155112</t>
+          <t>赫敏和罗恩</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>保密</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>我应该向老师们支付看视频的费用[保卫萝卜_哇]</t>
+          <t>来来来，送完这一把还有一把，再送完这把，还有三把</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -3261,14 +6579,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>480</v>
+        <v>10379</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-05 01:00:23</t>
+          <t>2025-03-16 22:11:58</t>
         </is>
       </c>
     </row>
@@ -3329,14 +6647,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>这视频看起来不太妙啊！</t>
+          <t>我和听泉合伙做了一门生意，但别人都说我们是骗子</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AAA钩子批发商第一世</t>
+          <t>潘仕学</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3346,7 +6664,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>所以整活挑战还录吗</t>
+          <t>感谢遇见南翔和听泉，虽然我们素不相识，从未谋面，但你们却毫不犹豫地伸出了援手。一次又一次，给我想办法，给我愁治病钱，这一份份沉甸甸的爱与希望，为我们照亮了前行的路，让我们有了继续为孩子治疗的勇气和力量。我们无以为报，只能在这里向你们表达最诚挚的感恩。谢谢你们在我们最艰难的时刻挺身而出，谢谢你们给予孩子生的希望。我们会永远铭记这份恩情，也会将这份爱传递下去，去帮助更多需要帮助的人。🙏🙏</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -3356,31 +6674,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>297</v>
+        <v>6834</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-03 20:17:48</t>
+          <t>2025-03-15 18:34:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>海露滴眼液</t>
+          <t>南翔不爱吃饭</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>保密</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>这视频看起来不太妙啊[哦呼]</t>
+          <t>有宝子们问怎么买老师的银饰、很抱歉老师目前只开通了某音的店铺（潘仕学非遗银饰）、阿b开店要10万粉，如果对潘老师的银饰有兴趣的话可以支持一下、在此谢过各位宝子了。因为银饰均属于手工制作，所以发货时间预计在7-15天内，辛苦宝子耐心可以等待几天[抱拳]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -3393,28 +6711,28 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>1908</v>
+        <v>13457</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-03 21:22:09</t>
+          <t>2025-03-14 18:33:51</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>纟工氵昷了</t>
+          <t>零钱之炼金术师</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>如果手上有倒刺的话建议用指甲刀剪掉别直接撕容易撕破💀(之前撕过破的地方疼的药似)</t>
+          <t>大家注意这种在街上很便宜卖你一个小东西的99.9%都是骗子，不是骗钱，大多数是骗你身份信息，或者恶意引导推广app的。某东经常这么干[doge_金箍]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -3424,14 +6742,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>219</v>
+        <v>716</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-04 21:34:01</t>
+          <t>2025-03-15 04:02:18</t>
         </is>
       </c>
     </row>
@@ -3492,14 +6810,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>骑老奶奶过马路的真人游戏就离谱</t>
+          <t>315曝光却成反向营销？蜜雪公关凭什么封神？</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>电次的恶魔套餐</t>
+          <t>独为你92</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3509,7 +6827,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>不是？最后一套呢？？？[doge][doge][doge]</t>
+          <t>315压根没提蜜雪冰城，是地方，好像是湖北还是哪提的，</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -3522,28 +6840,28 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>1017</v>
+        <v>882</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-03-04 16:55:16</t>
+          <t>2025-03-18 13:32:45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dawn-彤</t>
+          <t>香辣鸽寄_入夜狂飙</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>保密</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[笑哭]</t>
+          <t>这下没有隔夜柠檬了</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -3556,18 +6874,18 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>2090</v>
+        <v>182</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-03-04 18:45:40</t>
+          <t>2025-03-18 16:32:07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>无聊の穷龟</t>
+          <t>邬䵮</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3577,7 +6895,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新能源摩托-川崎grandma[doge]</t>
+          <t>此315非彼315，这个315是湖北经财弄的，说个题外话，湖北媒体不是第一次炮轰河南相关的东西了，大家熟知的极目新闻、楚天都市报等等</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -3587,14 +6905,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-03-04 17:03:20</t>
+          <t>2025-03-18 15:31:52</t>
         </is>
       </c>
     </row>
